--- a/data/fv_norms.xlsx
+++ b/data/fv_norms.xlsx
@@ -18,55 +18,75 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>f0_min</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>f0_max</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>v0_min</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>v0_max</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>f0_median</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>v0_median</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>raw_n</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>used_n</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>f0_mean</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>v0_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>f0_p25</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>f0_p75</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>v0_p25</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>v0_p75</t>
         </is>
@@ -79,38 +99,50 @@
         </is>
       </c>
       <c r="B2">
+        <v>6.24</v>
+      </c>
+      <c r="C2">
+        <v>8.82</v>
+      </c>
+      <c r="D2">
+        <v>7.97</v>
+      </c>
+      <c r="E2">
+        <v>10.49</v>
+      </c>
+      <c r="F2">
         <v>7.54</v>
       </c>
-      <c r="C2">
+      <c r="G2">
         <v>9.297224</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>quadrant_reference=median; raw_n=789; used_n=765; excluded_outliers=24; outlier_method=iqr_1.5</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="I2">
         <v>789</v>
       </c>
-      <c r="F2">
+      <c r="J2">
         <v>765</v>
       </c>
-      <c r="G2">
+      <c r="K2">
         <v>7.537869</v>
       </c>
-      <c r="H2">
+      <c r="L2">
         <v>9.287385</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>7.225664</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>7.85</v>
       </c>
-      <c r="K2">
+      <c r="O2">
         <v>8.95</v>
       </c>
-      <c r="L2">
+      <c r="P2">
         <v>9.61</v>
       </c>
     </row>
@@ -121,38 +153,50 @@
         </is>
       </c>
       <c r="B3">
+        <v>6.175621</v>
+      </c>
+      <c r="C3">
+        <v>8.887661</v>
+      </c>
+      <c r="D3">
+        <v>7.86</v>
+      </c>
+      <c r="E3">
+        <v>10.21</v>
+      </c>
+      <c r="F3">
         <v>7.518577</v>
       </c>
-      <c r="C3">
+      <c r="G3">
         <v>9.06</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>quadrant_reference=median; raw_n=730; used_n=704; excluded_outliers=26; outlier_method=iqr_1.5</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="I3">
         <v>730</v>
       </c>
-      <c r="F3">
+      <c r="J3">
         <v>704</v>
       </c>
-      <c r="G3">
+      <c r="K3">
         <v>7.508684</v>
       </c>
-      <c r="H3">
+      <c r="L3">
         <v>9.054647</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>7.17</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>7.847893</v>
       </c>
-      <c r="K3">
+      <c r="O3">
         <v>8.77</v>
       </c>
-      <c r="L3">
+      <c r="P3">
         <v>9.353806</v>
       </c>
     </row>
@@ -163,38 +207,50 @@
         </is>
       </c>
       <c r="B4">
+        <v>5.76</v>
+      </c>
+      <c r="C4">
+        <v>8.65</v>
+      </c>
+      <c r="D4">
+        <v>6.84</v>
+      </c>
+      <c r="E4">
+        <v>10.07</v>
+      </c>
+      <c r="F4">
         <v>7.214383</v>
       </c>
-      <c r="C4">
+      <c r="G4">
         <v>8.45</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>quadrant_reference=median; raw_n=756; used_n=739; excluded_outliers=17; outlier_method=iqr_1.5</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="I4">
         <v>756</v>
       </c>
-      <c r="F4">
+      <c r="J4">
         <v>739</v>
       </c>
-      <c r="G4">
+      <c r="K4">
         <v>7.208153</v>
       </c>
-      <c r="H4">
+      <c r="L4">
         <v>8.441461</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>6.861956</v>
       </c>
-      <c r="J4">
+      <c r="N4">
         <v>7.568408</v>
       </c>
-      <c r="K4">
+      <c r="O4">
         <v>8.033489</v>
       </c>
-      <c r="L4">
+      <c r="P4">
         <v>8.839114</v>
       </c>
     </row>
@@ -205,38 +261,50 @@
         </is>
       </c>
       <c r="B5">
+        <v>5.97</v>
+      </c>
+      <c r="C5">
+        <v>8.79</v>
+      </c>
+      <c r="D5">
+        <v>7.35</v>
+      </c>
+      <c r="E5">
+        <v>10.24</v>
+      </c>
+      <c r="F5">
         <v>7.39</v>
       </c>
-      <c r="C5">
+      <c r="G5">
         <v>8.843807</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>quadrant_reference=median; raw_n=801; used_n=781; excluded_outliers=20; outlier_method=iqr_1.5</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="I5">
         <v>801</v>
       </c>
-      <c r="F5">
+      <c r="J5">
         <v>781</v>
       </c>
-      <c r="G5">
+      <c r="K5">
         <v>7.375339</v>
       </c>
-      <c r="H5">
+      <c r="L5">
         <v>8.824092</v>
       </c>
-      <c r="I5">
+      <c r="M5">
         <v>7.0</v>
       </c>
-      <c r="J5">
+      <c r="N5">
         <v>7.72</v>
       </c>
-      <c r="K5">
+      <c r="O5">
         <v>8.47</v>
       </c>
-      <c r="L5">
+      <c r="P5">
         <v>9.19</v>
       </c>
     </row>
@@ -247,38 +315,50 @@
         </is>
       </c>
       <c r="B6">
+        <v>5.587084</v>
+      </c>
+      <c r="C6">
+        <v>8.314262</v>
+      </c>
+      <c r="D6">
+        <v>6.31</v>
+      </c>
+      <c r="E6">
+        <v>9.28</v>
+      </c>
+      <c r="F6">
         <v>6.944341</v>
       </c>
-      <c r="C6">
+      <c r="G6">
         <v>7.760459</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>quadrant_reference=median; raw_n=738; used_n=724; excluded_outliers=14; outlier_method=iqr_1.5</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="I6">
         <v>738</v>
       </c>
-      <c r="F6">
+      <c r="J6">
         <v>724</v>
       </c>
-      <c r="G6">
+      <c r="K6">
         <v>6.925981</v>
       </c>
-      <c r="H6">
+      <c r="L6">
         <v>7.809003</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>6.587747</v>
       </c>
-      <c r="J6">
+      <c r="N6">
         <v>7.29</v>
       </c>
-      <c r="K6">
+      <c r="O6">
         <v>7.42139</v>
       </c>
-      <c r="L6">
+      <c r="P6">
         <v>8.21</v>
       </c>
     </row>
@@ -289,38 +369,50 @@
         </is>
       </c>
       <c r="B7">
+        <v>6.478287</v>
+      </c>
+      <c r="C7">
+        <v>8.569166</v>
+      </c>
+      <c r="D7">
+        <v>9.039046</v>
+      </c>
+      <c r="E7">
+        <v>10.38895</v>
+      </c>
+      <c r="F7">
         <v>7.616972</v>
       </c>
-      <c r="C7">
+      <c r="G7">
         <v>9.71861</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>quadrant_reference=median; raw_n=69; used_n=65; excluded_outliers=4; outlier_method=iqr_1.5</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="I7">
         <v>69</v>
       </c>
-      <c r="F7">
+      <c r="J7">
         <v>65</v>
       </c>
-      <c r="G7">
+      <c r="K7">
         <v>7.623259</v>
       </c>
-      <c r="H7">
+      <c r="L7">
         <v>9.723415</v>
       </c>
-      <c r="I7">
+      <c r="M7">
         <v>7.322521</v>
       </c>
-      <c r="J7">
+      <c r="N7">
         <v>7.929365</v>
       </c>
-      <c r="K7">
+      <c r="O7">
         <v>9.504824</v>
       </c>
-      <c r="L7">
+      <c r="P7">
         <v>9.978732</v>
       </c>
     </row>
